--- a/fake_db/MP_db.xlsx
+++ b/fake_db/MP_db.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>Gene</t>
   </si>
@@ -54,6 +54,12 @@
   </si>
   <si>
     <t>NM_00180448.3:exon11&gt;c.133_135delinsTGT:p.(R45C)</t>
+  </si>
+  <si>
+    <t>NUP93</t>
+  </si>
+  <si>
+    <t>NM_014669.5:exon2:c.41_42inv:p.(E14V)</t>
   </si>
 </sst>
 </file>
@@ -1217,8 +1223,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="1"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="6.54545454545455" customWidth="1"/>
     <col min="2" max="2" width="54.5454545454545" customWidth="1"/>
@@ -1270,6 +1276,14 @@
       </c>
       <c r="B6" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
